--- a/data/trans_dic/IP19C07-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por ortodoncia</t>
+          <t>Menores que en su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,02</t>
+          <t>0,0; 74,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,81</t>
+          <t>0,0; 53,24</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 4,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,01</t>
+          <t>0,0; 5,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,35</t>
+          <t>0,0; 6,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,8</t>
+          <t>0,0; 5,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,97</t>
+          <t>0,74; 8,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,19</t>
+          <t>0,71; 6,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 7,58</t>
+          <t>0,51; 6,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,8</t>
+          <t>0,78; 5,18</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,48</t>
+          <t>0,76; 4,27</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 5,73</t>
+          <t>0,83; 5,87</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 16,65</t>
+          <t>6,41; 16,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 11,4</t>
+          <t>4,16; 11,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 5,7</t>
+          <t>0,84; 5,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,81</t>
+          <t>1,15; 6,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 8,7</t>
+          <t>2,04; 8,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 13,33</t>
+          <t>5,29; 13,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,98</t>
+          <t>1,87; 7,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 10,16</t>
+          <t>3,52; 10,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 10,95</t>
+          <t>5,11; 11,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,44; 10,94</t>
+          <t>5,6; 10,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,46</t>
+          <t>1,84; 5,57</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,06; 7,6</t>
+          <t>2,91; 8,13</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,28; 24,94</t>
+          <t>14,17; 24,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,58; 22,78</t>
+          <t>12,49; 22,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,87; 24,05</t>
+          <t>12,56; 23,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 17,77</t>
+          <t>8,65; 16,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,92; 22,11</t>
+          <t>12,97; 22,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,38; 21,1</t>
+          <t>10,47; 20,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,5; 14,05</t>
+          <t>5,74; 14,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 10,66</t>
+          <t>4,13; 10,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,09; 21,76</t>
+          <t>15,02; 21,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,0; 20,12</t>
+          <t>12,71; 19,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 17,0</t>
+          <t>10,15; 16,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,1; 12,39</t>
+          <t>7,25; 12,03</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 15,09</t>
+          <t>9,47; 15,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 12,55</t>
+          <t>7,26; 12,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,96; 11,05</t>
+          <t>5,88; 11,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,53</t>
+          <t>5,92; 10,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 12,91</t>
+          <t>7,5; 12,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,56; 12,71</t>
+          <t>7,66; 12,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,05</t>
+          <t>4,04; 7,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,86</t>
+          <t>4,0; 8,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 13,06</t>
+          <t>9,32; 13,24</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 11,88</t>
+          <t>8,05; 11,8</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,55; 8,62</t>
+          <t>5,43; 8,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,14; 8,24</t>
+          <t>5,21; 8,17</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por ortodoncia (tasa de respuesta: 99,51%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2904</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3088</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1480</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3046</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1984</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>3793</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2990</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3463</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3787</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3872</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4586</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4531</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>677; 7425</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>583; 5529</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>395; 5269</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4687</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>1319; 8791</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1141; 6412</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1186; 8411</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10980</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>8662</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3754</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3791</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4945</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11546</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6293</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>10300</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>15925</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>20208</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>10046</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>14091</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>6355; 16497</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5234; 14437</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1255; 8279</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1402; 8195</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2161; 8998</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6987; 17988</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2789; 11169</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>5797; 17793</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>10464; 22599</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>14451; 27876</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>5474; 16600</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>8346; 23302</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>31150</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>24929</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25256</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>25087</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>29960</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>21560</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>12295</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>15596</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>61110</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>46489</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>37551</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>40684</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>23160; 40125</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>18482; 33714</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>18326; 33752</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>17108; 33401</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>22532; 38907</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>14781; 29600</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>7768; 19011</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>9804; 24726</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>50651; 72627</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>36759; 57325</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>28522; 47083</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>31534; 52328</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>42898</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>34337</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>29692</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30358</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36227</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36153</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>27880</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>79125</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>70490</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>50587</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>58238</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>33248; 53716</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25757; 43994</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>21373; 39972</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>23186; 41294</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>27139; 45993</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>28052; 47275</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14857; 29276</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>19399; 38966</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>66442; 94353</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>58006; 85017</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>39744; 62906</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>45682; 71610</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C07-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Edad-trans_dic.xlsx
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,35</t>
+          <t>0,0; 71,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,24</t>
+          <t>0,0; 54,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -862,37 +862,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 4,87</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,69</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,93</t>
+          <t>0,0; 7,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,63</t>
+          <t>0,0; 5,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 8,06</t>
+          <t>0,73; 8,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,73</t>
+          <t>0,72; 6,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,83</t>
+          <t>0,51; 8,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,18</t>
+          <t>0,81; 4,87</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,27</t>
+          <t>0,74; 4,37</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,87</t>
+          <t>0,83; 5,61</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,41; 16,63</t>
+          <t>6,35; 17,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,16; 11,47</t>
+          <t>3,88; 11,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,56</t>
+          <t>0,84; 5,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,15; 6,72</t>
+          <t>1,19; 6,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 8,51</t>
+          <t>2,45; 9,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 13,62</t>
+          <t>5,38; 13,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,48</t>
+          <t>1,91; 7,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 10,8</t>
+          <t>3,44; 10,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 11,03</t>
+          <t>5,13; 11,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,6; 10,81</t>
+          <t>5,38; 10,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,84; 5,57</t>
+          <t>1,95; 5,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,13</t>
+          <t>3,0; 7,6</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,17; 24,54</t>
+          <t>14,9; 24,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,49; 22,79</t>
+          <t>12,9; 22,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,56; 23,14</t>
+          <t>12,13; 22,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,65; 16,89</t>
+          <t>8,8; 17,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,97; 22,4</t>
+          <t>13,04; 22,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,47; 20,97</t>
+          <t>10,82; 20,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 14,06</t>
+          <t>5,4; 13,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 10,42</t>
+          <t>3,97; 10,17</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 21,54</t>
+          <t>14,95; 21,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,71; 19,83</t>
+          <t>12,69; 19,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,15; 16,75</t>
+          <t>10,12; 17,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,25; 12,03</t>
+          <t>7,19; 12,44</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,47; 15,31</t>
+          <t>9,73; 15,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,26; 12,4</t>
+          <t>7,29; 12,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 11,0</t>
+          <t>5,93; 11,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,92; 10,54</t>
+          <t>5,64; 10,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,5; 12,71</t>
+          <t>7,79; 12,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,66; 12,92</t>
+          <t>7,58; 12,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,04; 7,96</t>
+          <t>3,94; 7,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,0; 8,04</t>
+          <t>4,12; 7,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,32; 13,24</t>
+          <t>9,35; 13,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,05; 11,8</t>
+          <t>8,09; 11,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,6</t>
+          <t>5,57; 8,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,21; 8,17</t>
+          <t>5,23; 8,22</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2904</t>
+          <t>0; 2809</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3088</t>
+          <t>0; 3166</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1858,57 +1858,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 3787</t>
+          <t>0; 4276</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3872</t>
+          <t>0; 3312</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4586</t>
+          <t>0; 4922</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4531</t>
+          <t>0; 4281</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>677; 7425</t>
+          <t>676; 7552</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>583; 5529</t>
+          <t>587; 5637</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>395; 5269</t>
+          <t>391; 6371</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4687</t>
+          <t>0; 4674</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1319; 8791</t>
+          <t>1379; 8267</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1141; 6412</t>
+          <t>1106; 6562</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1186; 8411</t>
+          <t>1189; 8039</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6355; 16497</t>
+          <t>6302; 17333</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5234; 14437</t>
+          <t>4884; 14808</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1255; 8279</t>
+          <t>1253; 8649</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1402; 8195</t>
+          <t>1446; 8259</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2161; 8998</t>
+          <t>2591; 9885</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6987; 17988</t>
+          <t>7102; 17516</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2789; 11169</t>
+          <t>2850; 10563</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5797; 17793</t>
+          <t>5674; 17435</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10464; 22599</t>
+          <t>10522; 22848</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14451; 27876</t>
+          <t>13888; 27633</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5474; 16600</t>
+          <t>5806; 15868</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8346; 23302</t>
+          <t>8604; 21778</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23160; 40125</t>
+          <t>24363; 40729</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18482; 33714</t>
+          <t>19080; 33765</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18326; 33752</t>
+          <t>17690; 33393</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17108; 33401</t>
+          <t>17403; 34692</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22532; 38907</t>
+          <t>22650; 39249</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14781; 29600</t>
+          <t>15281; 28817</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7768; 19011</t>
+          <t>7297; 18266</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9804; 24726</t>
+          <t>9414; 24123</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50651; 72627</t>
+          <t>50424; 73364</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36759; 57325</t>
+          <t>36691; 56995</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28522; 47083</t>
+          <t>28459; 48404</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31534; 52328</t>
+          <t>31272; 54113</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33248; 53716</t>
+          <t>34135; 53121</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25757; 43994</t>
+          <t>25853; 43860</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21373; 39972</t>
+          <t>21548; 39995</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23186; 41294</t>
+          <t>22072; 41057</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27139; 45993</t>
+          <t>28173; 46308</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28052; 47275</t>
+          <t>27746; 46738</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14857; 29276</t>
+          <t>14488; 28954</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19399; 38966</t>
+          <t>19975; 38241</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>66442; 94353</t>
+          <t>66619; 94096</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58006; 85017</t>
+          <t>58317; 84678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>39744; 62906</t>
+          <t>40738; 63133</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45682; 71610</t>
+          <t>45816; 72029</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C07-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP19C07-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,27 +649,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>19,67%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 71,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -737,27 +737,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 77,02</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,6</t>
+          <t>0,0; 58,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,81%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,75; 7,97</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,73; 7,19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,45; 7,93</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,5</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,87</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,44</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,32</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 8,2</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,86</t>
+          <t>0,0; 6,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 8,26</t>
+          <t>0,0; 7,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,87</t>
+          <t>0,76; 4,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,37</t>
+          <t>0,74; 4,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 5,61</t>
+          <t>0,75; 5,95</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6,68%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>11,07%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>6,88%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,52%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,68%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 17,47</t>
+          <t>1,87; 8,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 11,77</t>
+          <t>5,33; 13,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,81</t>
+          <t>1,93; 7,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,77</t>
+          <t>3,63; 10,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,45; 9,35</t>
+          <t>6,53; 16,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 13,26</t>
+          <t>3,85; 11,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,07</t>
+          <t>0,81; 5,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,44; 10,58</t>
+          <t>1,21; 6,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 11,15</t>
+          <t>4,9; 10,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,38; 10,71</t>
+          <t>5,44; 10,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,32</t>
+          <t>1,91; 5,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 7,6</t>
+          <t>3,21; 7,71</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>17,25%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15,27%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>19,05%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>16,85%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>17,31%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,9; 24,91</t>
+          <t>12,92; 22,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,9; 22,83</t>
+          <t>11,38; 21,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,13; 22,89</t>
+          <t>5,5; 14,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 17,54</t>
+          <t>4,29; 10,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,04; 22,6</t>
+          <t>14,28; 24,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,82; 20,41</t>
+          <t>12,58; 22,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,4; 13,5</t>
+          <t>12,87; 24,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,97; 10,17</t>
+          <t>8,86; 18,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,95; 21,76</t>
+          <t>15,09; 21,76</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12,69; 19,71</t>
+          <t>13,0; 20,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,12; 17,22</t>
+          <t>10,27; 17,0</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 12,44</t>
+          <t>7,32; 12,79</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>12,22%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>9,68%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>8,17%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>10,01%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>9,88%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,93%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 15,14</t>
+          <t>7,67; 12,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 12,36</t>
+          <t>7,56; 12,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,93; 11,01</t>
+          <t>4,08; 8,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,64; 10,48</t>
+          <t>4,29; 8,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 12,8</t>
+          <t>9,37; 15,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,58; 12,77</t>
+          <t>7,43; 12,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,87</t>
+          <t>5,96; 11,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,12; 7,89</t>
+          <t>5,77; 10,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>9,35; 13,2</t>
+          <t>9,16; 13,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,09; 11,75</t>
+          <t>8,1; 11,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,57; 8,63</t>
+          <t>5,55; 8,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,22</t>
+          <t>5,31; 8,52</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,27 +1509,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1577,27 +1577,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>768</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2809</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1665,27 +1665,27 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>0; 3008</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3166</t>
+          <t>0; 3410</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,49 +1785,49 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3046</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1724</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>747</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>682</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1480</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1321</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3046</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2308</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1984</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>3793</t>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3463</t>
+          <t>3112</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0; 4661</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>694; 7335</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>599; 5907</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>305; 5360</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4276</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3312</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4922</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4281</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>676; 7552</t>
+          <t>0; 3743</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>587; 5637</t>
+          <t>0; 4089</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>391; 6371</t>
+          <t>0; 5001</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4674</t>
+          <t>0; 4342</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1379; 8267</t>
+          <t>1296; 8155</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1106; 6562</t>
+          <t>1119; 6725</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1189; 8039</t>
+          <t>982; 7791</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4945</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11546</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6293</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10381</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>10980</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>8662</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>3754</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3791</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4945</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11546</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6293</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10300</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14091</t>
+          <t>14012</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6302; 17333</t>
+          <t>1973; 9194</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4884; 14808</t>
+          <t>7043; 17613</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1253; 8649</t>
+          <t>2884; 11918</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1446; 8259</t>
+          <t>5638; 16753</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2591; 9885</t>
+          <t>6473; 16515</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7102; 17516</t>
+          <t>4849; 14339</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2850; 10563</t>
+          <t>1207; 8487</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5674; 17435</t>
+          <t>1468; 8099</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10522; 22848</t>
+          <t>10040; 22435</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13888; 27633</t>
+          <t>14037; 28207</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5806; 15868</t>
+          <t>5708; 16288</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8604; 21778</t>
+          <t>8903; 21366</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>29960</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21560</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12295</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15808</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>31150</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>24929</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>25256</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25087</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>29960</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21560</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12295</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>15596</t>
+          <t>26451</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40684</t>
+          <t>42259</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24363; 40729</t>
+          <t>22441; 38405</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19080; 33765</t>
+          <t>16063; 29792</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17690; 33393</t>
+          <t>7438; 18999</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17403; 34692</t>
+          <t>10014; 25434</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22650; 39249</t>
+          <t>23344; 40776</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15281; 28817</t>
+          <t>18611; 33692</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7297; 18266</t>
+          <t>18780; 35084</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9414; 24123</t>
+          <t>18150; 37381</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>50424; 73364</t>
+          <t>50871; 73358</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36691; 56995</t>
+          <t>37594; 58179</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28459; 48404</t>
+          <t>28875; 47786</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>31272; 54113</t>
+          <t>32094; 56080</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>36227</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>36153</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20895</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>27914</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>42898</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>34337</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>29692</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30358</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>36227</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36153</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20895</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>27880</t>
+          <t>31469</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>58238</t>
+          <t>59383</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34135; 53121</t>
+          <t>27746; 46699</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>25853; 43860</t>
+          <t>27652; 46512</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>21548; 39995</t>
+          <t>15014; 29636</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22072; 41057</t>
+          <t>19800; 38307</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>28173; 46308</t>
+          <t>32872; 52969</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27746; 46738</t>
+          <t>26370; 44516</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14488; 28954</t>
+          <t>21653; 40170</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>19975; 38241</t>
+          <t>22847; 42910</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>66619; 94096</t>
+          <t>65315; 93057</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>58317; 84678</t>
+          <t>58351; 85608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40738; 63133</t>
+          <t>40567; 63057</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45816; 72029</t>
+          <t>45499; 73060</t>
         </is>
       </c>
     </row>
